--- a/scenarios/06_dr_chen_researcher/6.3_noise_model_verification/outputs/verification_results.xlsx
+++ b/scenarios/06_dr_chen_researcher/6.3_noise_model_verification/outputs/verification_results.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -474,12 +474,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Hand Calc [e⁻ RMS]</t>
+          <t>Hand Calc [e- RMS]</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>RADIANT [e⁻ RMS]</t>
+          <t>RADIANT [e- RMS]</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>e⁻ RMS</t>
+          <t>e- RMS</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -538,7 +538,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>e⁻ RMS</t>
+          <t>e- RMS</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>704.9252</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>725.7956</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>e⁻ RMS</t>
+          <t>e- RMS</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>e⁻ RMS</t>
+          <t>e- RMS</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -616,7 +616,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>e⁻ RMS</t>
+          <t>e- RMS</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -642,7 +642,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>e⁻ RMS</t>
+          <t>e- RMS</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -661,18 +661,18 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1704.151</v>
+        <v>1551.5189</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1754.029</v>
+        <v>1596.8213</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>e⁻ RMS</t>
+          <t>e- RMS</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="12">
@@ -716,18 +716,18 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>858.71</v>
+        <v>943.25</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>835.33</v>
+        <v>917.5</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>— (dimensionless)</t>
+          <t>-- (dimensionless)</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="15">
@@ -737,36 +737,179 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>263.95</v>
+        <v>289.93</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>--</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>— (dimensionless)</t>
+          <t>-- (dimensionless)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>NEDT</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>mK</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>7.37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>NIIRS</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>-- (dimensionless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>GSD (geometric mean)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>MTF at Nyquist</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>0.4223</v>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>— (dimensionless)</t>
+      <c r="B19" s="3" t="n">
+        <v>0.2532</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>-- (dimensionless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Strehl ratio</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>-- (dimensionless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Q (sampling parameter)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>-- (dimensionless)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>EE (1x1 pixel)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>-- (fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Well margin</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>dB</t>
         </is>
       </c>
     </row>
